--- a/data/trans_dic/P57B_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P57B_R-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con bienestar emocional por debajo del percentil 15 (Bericat)</t>
+          <t>Población con peor bienestar socioemocional (percentil 15) (Bericat) (tasa de respuesta: 98,25%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,08; 25,62</t>
+          <t>19,14; 26,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,55; 32,81</t>
+          <t>27,57; 32,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24,94; 28,86</t>
+          <t>25,07; 29,0</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,21; 8,92</t>
+          <t>5,21; 8,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,66; 11,12</t>
+          <t>7,06; 11,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,77; 9,65</t>
+          <t>6,62; 9,76</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,46; 8,76</t>
+          <t>4,48; 8,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,07; 10,75</t>
+          <t>7,08; 10,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,27; 8,91</t>
+          <t>6,32; 9,14</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,42; 10,64</t>
+          <t>7,39; 10,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,25; 14,96</t>
+          <t>11,01; 14,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,93; 12,48</t>
+          <t>9,93; 12,55</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con bienestar emocional por debajo del percentil 15 (Bericat)</t>
+          <t>Población con peor bienestar socioemocional (percentil 15) (Bericat) (tasa de respuesta: 98,25%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>95563; 128283</t>
+          <t>95868; 130561</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>199940; 238163</t>
+          <t>200094; 234050</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>305933; 354024</t>
+          <t>307481; 355766</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>117993; 202099</t>
+          <t>117961; 202338</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>147610; 246259</t>
+          <t>156384; 246458</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>303094; 432420</t>
+          <t>296380; 437106</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>28686; 56296</t>
+          <t>28766; 57022</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>46443; 70647</t>
+          <t>46477; 71761</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>81461; 115754</t>
+          <t>82086; 118774</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>252816; 362640</t>
+          <t>251946; 364659</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>404852; 538177</t>
+          <t>395905; 534862</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>695377; 874319</t>
+          <t>695907; 879267</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P57B_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P57B_R-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,75%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,14; 26,07</t>
+          <t>18,68; 25,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,57; 32,24</t>
+          <t>27,54; 32,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,07; 29,0</t>
+          <t>24,81; 28,72</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,21; 8,93</t>
+          <t>7,37; 9,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,06; 11,13</t>
+          <t>10,03; 12,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,62; 9,76</t>
+          <t>9,02; 10,67</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,48; 8,87</t>
+          <t>4,74; 8,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,08; 10,92</t>
+          <t>6,81; 10,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,32; 9,14</t>
+          <t>6,08; 8,85</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>12,54%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,39; 10,7</t>
+          <t>9,24; 11,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,01; 14,87</t>
+          <t>13,83; 15,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,93; 12,55</t>
+          <t>11,85; 13,27</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>111707</t>
+          <t>122305</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>217768</t>
+          <t>238412</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>329475</t>
+          <t>360717</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>95868; 130561</t>
+          <t>104379; 140384</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>200094; 234050</t>
+          <t>217554; 258202</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>307481; 355766</t>
+          <t>334663; 387313</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>170209</t>
+          <t>187335</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>211102</t>
+          <t>239726</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>381311</t>
+          <t>427060</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>117961; 202338</t>
+          <t>162492; 215436</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>156384; 246458</t>
+          <t>215164; 265172</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>296380; 437106</t>
+          <t>392550; 463914</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40527</t>
+          <t>44978</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>57520</t>
+          <t>62186</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>98047</t>
+          <t>107165</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>28766; 57022</t>
+          <t>33506; 61566</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>46477; 71761</t>
+          <t>49766; 76747</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>82086; 118774</t>
+          <t>87493; 127306</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>322443</t>
+          <t>354618</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>486390</t>
+          <t>540324</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>808833</t>
+          <t>894942</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>251946; 364659</t>
+          <t>320755; 390738</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>395905; 534862</t>
+          <t>506880; 576044</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>695907; 879267</t>
+          <t>845743; 946919</t>
         </is>
       </c>
     </row>
